--- a/data/baidu/china_noir.xlsx
+++ b/data/baidu/china_noir.xlsx
@@ -583,16 +583,24 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 4193152057, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>死尸死时四十四</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>死尸死时四十四</t>
+        </is>
+      </c>
       <c r="T2" t="n">
         <v>0</v>
       </c>
@@ -660,16 +668,24 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>纪录片：流血的黄色录像</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>纪录片</t>
+        </is>
+      </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
@@ -737,16 +753,24 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>武松打我</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>武松打我</t>
+        </is>
+      </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
@@ -814,16 +838,24 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>黑活儿</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>黑活儿</t>
+        </is>
+      </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
@@ -888,24 +920,30 @@
           <t>https://movie.douban.com/subject/30145577/</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>1290</v>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>不良街区</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>不良街区</t>
+        </is>
+      </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -968,16 +1006,24 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 4193696214, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>满洲里来的人</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>满洲里来的人</t>
+        </is>
+      </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
